--- a/GitHub_AltData_Pipeline/github_data.xlsx
+++ b/GitHub_AltData_Pipeline/github_data.xlsx
@@ -3648,7 +3648,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>89765</v>
+        <v>89767</v>
       </c>
       <c r="E112" t="n">
-        <v>39228</v>
+        <v>39229</v>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.052803+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.052803+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -10411,14 +10411,14 @@
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G332" t="n">
         <v>1</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>51269</v>
+        <v>51264</v>
       </c>
       <c r="E334" t="n">
         <v>22088</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.052803+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -13749,14 +13749,14 @@
       <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G443" t="n">
         <v>1</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.052803+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.114749+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>14945</v>
+        <v>14944</v>
       </c>
       <c r="E556" t="n">
         <v>5789</v>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.052803+00:00</t>
+          <t>2026-08-04T05:55:39.287504+00:00</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17285,7 +17285,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17318,7 +17318,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17351,7 +17351,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17421,7 +17421,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17493,7 +17493,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17789,7 +17789,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17826,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18492,7 +18492,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18603,7 +18603,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18640,7 +18640,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18936,7 +18936,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19010,7 +19010,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19232,7 +19232,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19269,7 +19269,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19676,7 +19676,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19750,7 +19750,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19861,7 +19861,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20157,7 +20157,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20268,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20379,7 +20379,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20564,7 +20564,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20749,7 +20749,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20786,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21082,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21152,7 +21152,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21218,7 +21218,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21242,7 @@
         <v>89747</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F111" t="n">
         <v>89742</v>
@@ -21251,7 +21251,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
         <v>89765</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F113" t="n">
         <v>89749.66666666667</v>
@@ -21317,7 +21317,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21338,19 +21338,19 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>39228</v>
+        <v>39229</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9482758620689655</v>
       </c>
       <c r="F114" t="n">
-        <v>39205.5</v>
+        <v>39205.75</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21371,19 +21371,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>89765</v>
+        <v>89767</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>89753.5</v>
+        <v>89754</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21416,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21449,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21482,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21515,7 +21515,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21768,7 +21768,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21842,7 +21842,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21879,7 +21879,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22175,7 +22175,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22212,7 +22212,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22249,7 +22249,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22323,7 +22323,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22471,7 +22471,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22693,7 +22693,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22730,7 +22730,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22878,7 +22878,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22915,7 +22915,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23026,7 +23026,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23063,7 +23063,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23285,7 +23285,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23322,7 +23322,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23396,7 +23396,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23544,7 +23544,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23655,7 +23655,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23840,7 +23840,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23914,7 +23914,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24025,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24062,7 +24062,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24099,7 +24099,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24173,7 +24173,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24321,7 +24321,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24358,7 +24358,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24395,7 +24395,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24432,7 +24432,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24469,7 +24469,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24765,7 +24765,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24876,7 +24876,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25059,7 +25059,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25133,7 +25133,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25170,7 +25170,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25205,7 +25205,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25242,7 +25242,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25279,7 +25279,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25345,7 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25411,7 +25411,7 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25444,7 +25444,7 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25477,7 +25477,7 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25510,7 +25510,7 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25576,7 +25576,7 @@
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25609,7 +25609,7 @@
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25642,7 +25642,7 @@
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25675,7 +25675,7 @@
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25710,7 +25710,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25745,7 +25745,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25817,7 +25817,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25854,7 +25854,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25928,7 +25928,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -25965,7 +25965,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26039,7 +26039,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26187,7 +26187,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26224,7 +26224,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26298,7 +26298,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26372,7 +26372,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26483,7 +26483,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26557,7 +26557,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26594,7 +26594,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26629,7 +26629,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26666,7 +26666,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26703,7 +26703,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26740,7 +26740,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26814,7 +26814,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26888,7 +26888,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26925,7 +26925,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26962,7 +26962,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27036,7 +27036,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27184,7 +27184,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27258,7 +27258,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27295,7 +27295,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27332,7 +27332,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27369,7 +27369,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27443,7 +27443,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27480,7 +27480,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27554,7 +27554,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27591,7 +27591,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27628,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27702,7 +27702,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27739,7 +27739,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27776,7 +27776,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27813,7 +27813,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27850,7 +27850,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27887,7 +27887,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27924,7 +27924,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28035,7 +28035,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28072,7 +28072,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28109,7 +28109,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28294,7 +28294,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28405,7 +28405,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28442,7 +28442,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28516,7 +28516,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28553,7 +28553,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28590,7 +28590,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28701,7 +28701,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28738,7 +28738,7 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28923,7 +28923,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28960,7 +28960,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29034,7 +29034,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29071,7 +29071,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29108,7 +29108,7 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29145,7 +29145,7 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29182,7 +29182,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29256,7 +29256,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29293,7 +29293,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29330,7 +29330,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29367,7 +29367,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29404,7 +29404,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29441,7 +29441,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29474,7 +29474,7 @@
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29507,7 +29507,7 @@
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29540,7 +29540,7 @@
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
         <v>51252</v>
       </c>
       <c r="E339" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F339" t="n">
         <v>51249</v>
@@ -29573,7 +29573,7 @@
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29606,7 +29606,7 @@
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29630,7 +29630,7 @@
         <v>51267</v>
       </c>
       <c r="E341" t="n">
-        <v>0.9130434782608695</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
         <v>51255</v>
@@ -29639,7 +29639,7 @@
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29672,7 +29672,7 @@
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29693,19 +29693,19 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>51269</v>
+        <v>51264</v>
       </c>
       <c r="E343" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F343" t="n">
-        <v>51258.5</v>
+        <v>51257.25</v>
       </c>
       <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29738,7 +29738,7 @@
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29804,7 +29804,7 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29837,7 +29837,7 @@
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29907,7 +29907,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -29979,7 +29979,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30125,7 +30125,7 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30162,7 +30162,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30199,7 +30199,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30236,7 +30236,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30308,7 +30308,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30345,7 +30345,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30380,7 +30380,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30452,7 +30452,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30563,7 +30563,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30600,7 +30600,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30674,7 +30674,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30709,7 +30709,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30746,7 +30746,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30781,7 +30781,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30818,7 +30818,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30855,7 +30855,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -30966,7 +30966,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31003,7 +31003,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31188,7 +31188,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31225,7 +31225,7 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31262,7 +31262,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31336,7 +31336,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31445,7 +31445,7 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31556,7 +31556,7 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31630,7 +31630,7 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31704,7 +31704,7 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31741,7 +31741,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31815,7 +31815,7 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -31963,7 +31963,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32037,7 +32037,7 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32074,7 +32074,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32111,7 +32111,7 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32148,7 +32148,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32185,7 +32185,7 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32259,7 +32259,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32296,7 +32296,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32333,7 +32333,7 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32370,7 +32370,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32407,7 +32407,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32444,7 +32444,7 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32481,7 +32481,7 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32518,7 +32518,7 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32666,7 +32666,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32740,7 +32740,7 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32851,7 +32851,7 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32888,7 +32888,7 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -32999,7 +32999,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33073,7 +33073,7 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33147,7 +33147,7 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33184,7 +33184,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33295,7 +33295,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33369,7 +33369,7 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33443,7 +33443,7 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33480,7 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33517,7 +33517,7 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33554,7 +33554,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33624,7 +33624,7 @@
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33657,7 +33657,7 @@
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33690,7 +33690,7 @@
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33723,7 +33723,7 @@
       <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33756,7 +33756,7 @@
       <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33789,7 +33789,7 @@
       <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33822,7 +33822,7 @@
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33855,7 +33855,7 @@
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33888,7 +33888,7 @@
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33921,7 +33921,7 @@
       <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33954,7 +33954,7 @@
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -33987,7 +33987,7 @@
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34020,7 @@
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34053,7 +34053,7 @@
       <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34119,7 +34119,7 @@
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34152,7 +34152,7 @@
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34185,7 +34185,7 @@
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34218,7 +34218,7 @@
       <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34251,7 +34251,7 @@
       <c r="H469" t="inlineStr"/>
       <c r="I469" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34284,7 +34284,7 @@
       <c r="H470" t="inlineStr"/>
       <c r="I470" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34317,7 +34317,7 @@
       <c r="H471" t="inlineStr"/>
       <c r="I471" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34350,7 +34350,7 @@
       <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       <c r="H473" t="inlineStr"/>
       <c r="I473" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34416,7 +34416,7 @@
       <c r="H474" t="inlineStr"/>
       <c r="I474" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34449,7 +34449,7 @@
       <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34482,7 +34482,7 @@
       <c r="H476" t="inlineStr"/>
       <c r="I476" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34515,7 +34515,7 @@
       <c r="H477" t="inlineStr"/>
       <c r="I477" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34548,7 +34548,7 @@
       <c r="H478" t="inlineStr"/>
       <c r="I478" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34581,7 +34581,7 @@
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       <c r="H480" t="inlineStr"/>
       <c r="I480" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34647,7 +34647,7 @@
       <c r="H481" t="inlineStr"/>
       <c r="I481" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       <c r="H482" t="inlineStr"/>
       <c r="I482" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34713,7 +34713,7 @@
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34748,7 +34748,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34783,7 +34783,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34853,7 +34853,7 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -34995,7 +34995,7 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35065,7 +35065,7 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35100,7 +35100,7 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35170,7 +35170,7 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35275,7 +35275,7 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35310,7 +35310,7 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35345,7 +35345,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35380,7 +35380,7 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35415,7 +35415,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35450,7 +35450,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35485,7 +35485,7 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35520,7 +35520,7 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35590,7 +35590,7 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35695,7 +35695,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35730,7 +35730,7 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35765,7 +35765,7 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35798,7 +35798,7 @@
       <c r="H514" t="inlineStr"/>
       <c r="I514" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35831,7 +35831,7 @@
       <c r="H515" t="inlineStr"/>
       <c r="I515" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35864,7 +35864,7 @@
       <c r="H516" t="inlineStr"/>
       <c r="I516" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35897,7 +35897,7 @@
       <c r="H517" t="inlineStr"/>
       <c r="I517" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35930,7 +35930,7 @@
       <c r="H518" t="inlineStr"/>
       <c r="I518" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35963,7 +35963,7 @@
       <c r="H519" t="inlineStr"/>
       <c r="I519" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -35996,7 +35996,7 @@
       <c r="H520" t="inlineStr"/>
       <c r="I520" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36029,7 +36029,7 @@
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36062,7 +36062,7 @@
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36095,7 @@
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36128,7 +36128,7 @@
       <c r="H524" t="inlineStr"/>
       <c r="I524" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       <c r="H525" t="inlineStr"/>
       <c r="I525" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36194,7 +36194,7 @@
       <c r="H526" t="inlineStr"/>
       <c r="I526" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36227,7 +36227,7 @@
       <c r="H527" t="inlineStr"/>
       <c r="I527" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36260,7 +36260,7 @@
       <c r="H528" t="inlineStr"/>
       <c r="I528" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36293,7 +36293,7 @@
       <c r="H529" t="inlineStr"/>
       <c r="I529" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36326,7 +36326,7 @@
       <c r="H530" t="inlineStr"/>
       <c r="I530" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36359,7 +36359,7 @@
       <c r="H531" t="inlineStr"/>
       <c r="I531" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36392,7 +36392,7 @@
       <c r="H532" t="inlineStr"/>
       <c r="I532" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36425,7 +36425,7 @@
       <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36458,7 +36458,7 @@
       <c r="H534" t="inlineStr"/>
       <c r="I534" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36491,7 +36491,7 @@
       <c r="H535" t="inlineStr"/>
       <c r="I535" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36524,7 +36524,7 @@
       <c r="H536" t="inlineStr"/>
       <c r="I536" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36557,7 +36557,7 @@
       <c r="H537" t="inlineStr"/>
       <c r="I537" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36590,7 +36590,7 @@
       <c r="H538" t="inlineStr"/>
       <c r="I538" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36623,7 +36623,7 @@
       <c r="H539" t="inlineStr"/>
       <c r="I539" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36656,7 +36656,7 @@
       <c r="H540" t="inlineStr"/>
       <c r="I540" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36689,7 +36689,7 @@
       <c r="H541" t="inlineStr"/>
       <c r="I541" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36722,7 +36722,7 @@
       <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36755,7 +36755,7 @@
       <c r="H543" t="inlineStr"/>
       <c r="I543" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36788,7 +36788,7 @@
       <c r="H544" t="inlineStr"/>
       <c r="I544" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36821,7 +36821,7 @@
       <c r="H545" t="inlineStr"/>
       <c r="I545" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36854,7 +36854,7 @@
       <c r="H546" t="inlineStr"/>
       <c r="I546" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36887,7 +36887,7 @@
       <c r="H547" t="inlineStr"/>
       <c r="I547" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36920,7 +36920,7 @@
       <c r="H548" t="inlineStr"/>
       <c r="I548" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       <c r="H549" t="inlineStr"/>
       <c r="I549" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -36986,7 +36986,7 @@
       <c r="H550" t="inlineStr"/>
       <c r="I550" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37019,7 +37019,7 @@
       <c r="H551" t="inlineStr"/>
       <c r="I551" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37052,7 +37052,7 @@
       <c r="H552" t="inlineStr"/>
       <c r="I552" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37085,7 +37085,7 @@
       <c r="H553" t="inlineStr"/>
       <c r="I553" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37118,7 +37118,7 @@
       <c r="H554" t="inlineStr"/>
       <c r="I554" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       <c r="H555" t="inlineStr"/>
       <c r="I555" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37184,7 +37184,7 @@
       <c r="H556" t="inlineStr"/>
       <c r="I556" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37217,7 +37217,7 @@
       <c r="H557" t="inlineStr"/>
       <c r="I557" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37250,7 +37250,7 @@
       <c r="H558" t="inlineStr"/>
       <c r="I558" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37283,7 +37283,7 @@
       <c r="H559" t="inlineStr"/>
       <c r="I559" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37316,7 +37316,7 @@
       <c r="H560" t="inlineStr"/>
       <c r="I560" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37349,7 +37349,7 @@
       <c r="H561" t="inlineStr"/>
       <c r="I561" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37382,7 +37382,7 @@
       <c r="H562" t="inlineStr"/>
       <c r="I562" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       <c r="H563" t="inlineStr"/>
       <c r="I563" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37448,7 +37448,7 @@
       <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37481,7 +37481,7 @@
       <c r="H565" t="inlineStr"/>
       <c r="I565" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37514,7 +37514,7 @@
       <c r="H566" t="inlineStr"/>
       <c r="I566" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37547,7 +37547,7 @@
       <c r="H567" t="inlineStr"/>
       <c r="I567" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37580,7 +37580,7 @@
       <c r="H568" t="inlineStr"/>
       <c r="I568" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37613,7 +37613,7 @@
       <c r="H569" t="inlineStr"/>
       <c r="I569" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37646,7 +37646,7 @@
       <c r="H570" t="inlineStr"/>
       <c r="I570" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37667,19 +37667,19 @@
         </is>
       </c>
       <c r="D571" t="n">
-        <v>14945</v>
+        <v>14944</v>
       </c>
       <c r="E571" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F571" t="n">
-        <v>14944.25</v>
+        <v>14944</v>
       </c>
       <c r="G571" t="inlineStr"/>
       <c r="H571" t="inlineStr"/>
       <c r="I571" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.160892+00:00</t>
+          <t>2026-08-04T05:55:39.566260+00:00</t>
         </is>
       </c>
     </row>
@@ -37845,7 +37845,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121611+00:00</t>
+          <t>2026-08-04T05:55:39.539629+00:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -37926,7 +37926,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121588+00:00</t>
+          <t>2026-08-04T05:55:39.539612+00:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -37972,7 +37972,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>{"endpoint": "https://api.github.com/repos/bitcoin/bitcoin/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-04T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
+          <t>{"endpoint": "https://api.github.com/repos/bitcoin/bitcoin/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-05T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
         </is>
       </c>
     </row>
@@ -38088,7 +38088,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.104483+00:00</t>
+          <t>2026-08-04T05:55:39.539557+00:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -38134,7 +38134,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>{"id": 1181927, "node_id": "MDEwOlJlcG9zaXRvcnkxMTgxOTI3", "name": "bitcoin", "full_name": "bitcoin/bitcoin", "private": false, "owner": {"login": "bitcoin", "id": 528860, "node_id": "MDEyOk9yZ2FuaXphdGlvbjUyODg2MA==", "avatar_url": "https://avatars.githubusercontent.com/u/528860?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bitcoin", "html_url": "https://github.com/bitcoin", "followers_url": "https://api.github.com/users/bitcoin/followers", "following_url": "https://api.github.com/users/bitcoin/following{/other_user}", "gists_url": "https://api.github.com/users/bitcoin/gists{/gist_id}", "starred_url": "https://api.github.com/users/bitcoin/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bitcoin/subscriptions", "organizations_url": "https://api.github.com/users/bitcoin/orgs", "repos_url": "https://api.github.com/users/bitcoin/repos", "events_url": "https://api.github.com/users/bitcoin/events{/privacy}", "received_events_url": "https://api.github.com/users/bitcoin/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/bitcoin/bitcoin", "description": "Bitcoin Core integration/staging tree", "fork": false, "url": "https://api.github.com/repos/bitcoin/bitcoin", "forks_url": "https://api.github.com/repos/bitcoin/bitcoin/forks", "keys_url": "https://api.github.com/repos/bitcoin/bitcoin/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/bitcoin/bitcoin/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/bitcoin/bitcoin/teams", "hooks_url": "https://api.github.com/repos/bitcoin/bitcoin/hooks", "issue_events_url": "https://api.github.com/repos/bitcoin/bitcoin/issues/events{/number}", "events_url": "https://api.github.com/repos/bitcoin/bitcoin/events", "assignees_url": "https://api.github.com/repos/bitcoin/bitcoin/assignees{/user}", "branches_url": "https://api.github.com/repos/bitcoin/bitcoin/branches{/branch}", "tags_url": "https://api.github.com/repos/bitcoin/bitcoin/tags", "blobs_url": "https://api.github.com/repos/bitcoin/bitcoin/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/bitcoin/bitcoin/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/bitcoin/bitcoin/git/refs{/sha}", "trees_url": "https://api.github.com/repos/bitcoin/bitcoin/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/bitcoin/bitcoin/statuses/{sha}", "languages_url": "https://api.github.com/repos/bitcoin/bitcoin/languages", "stargazers_url": "https://api.github.com/repos/bitcoin/bitcoin/stargazers", "contributors_url": "https://api.github.com/repos/bitcoin/bitcoin/contributors", "subscribers_url": "https://api.github.com/repos/bitcoin/bitcoin/subscribers", "subscription_url": "https://api.github.com/repos/bitcoin/bitcoin/subscription", "commits_url": "https://api.github.com/repos/bitcoin/bitcoin/commits{/sha}", "git_commits_url": "https://api.github.com/repos/bitcoin/bitcoin/git/commits{/sha}", "comments_url": "https://api.github.com/repos/bitcoin/bitcoin/comments{/number}", "issue_comment_url": "https://api.github.com/repos/bitcoin/bitcoin/issues/comments{/number}", "contents_url": "https://api.github.com/repos/bitcoin/bitcoin/contents/{+path}", "compare_url": "https://api.github.com/repos/bitcoin/bitcoin/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/bitcoin/bitcoin/merges", "archive_url": "https://api.github.com/repos/bitcoin/bitcoin/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/bitcoin/bitcoin/downloads", "issues_url": "https://api.github.com/repos/bitcoin/bitcoin/issues{/number}", "pulls_url": "https://api.github.com/repos/bitcoin/bitcoin/pulls{/number}", "milestones_url": "https://api.github.com/repos/bitcoin/bitcoin/milestones{/number}", "notifications_url": "https://api.github.com/repos/bitcoin/bitcoin/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/bitcoin/bitcoin/labels{/name}", "releases_url": "https://api.github.com/repos/bitcoin/bitcoin/releases{/id}", "deployments_url": "https://api.github.com/repos/bitcoin/bitcoin/deployments", "created_at": "2010-12-19T15:16:43Z", "updated_at": "2026-08-03T17:03:37Z", "pushed_at": "2026-08-03T14:53:28Z", "git_url": "git://github.com/bitcoin/bitcoin.git", "ssh_url": "git@github.com:bitcoin/bitcoin.git", "clone_url": "https://github.com/bitcoin/bitcoin.git", "svn_url": "https://github.com/bitcoin/bitcoin", "homepage": "https://bitcoincore.org/en/download", "size": 321131, "stargazers_count": 89765, "watchers_count": 89765, "language": "C++", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": false, "has_pages": false, "has_discussions": false, "forks_count": 39228, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 697, "license": {"key": "mit", "name": "MIT License", "spdx_id": "MIT", "url": "https://api.github.com/licenses/mit", "node_id": "MDc6TGljZW5zZTEz"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["bitcoin", "c-plus-plus", "cryptocurrency", "cryptography", "p2p"], "visibility": "public", "forks": 39228, "open_issues": 697, "watchers": 89765, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": true}, "custom_properties": {}, "organization": {"login": "bitcoin", "id": 528860, "node_id": "MDEyOk9yZ2FuaXphdGlvbjUyODg2MA==", "avatar_url": "https://avatars.githubusercontent.com/u/528860?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bitcoin", "html_url": "https://github.com/bitcoin", "followers_url": "https://api.github.com/users/bitcoin/followers", "following_url": "https://api.github.com/users/bitcoin/following{/other_user}", "gists_url": "https://api.github.com/users/bitcoin/gists{/gist_id}", "starred_url": "https://api.github.com/users/bitcoin/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bitcoin/subscriptions", "organizations_url": "https://api.github.com/users/bitcoin/orgs", "repos_url": "https://api.github.com/users/bitcoin/repos", "events_url": "https://api.github.com/users/bitcoin/events{/privacy}", "received_events_url": "https://api.github.com/users/bitcoin/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 39228, "subscribers_count": 4101}</t>
+          <t>{"id": 1181927, "node_id": "MDEwOlJlcG9zaXRvcnkxMTgxOTI3", "name": "bitcoin", "full_name": "bitcoin/bitcoin", "private": false, "owner": {"login": "bitcoin", "id": 528860, "node_id": "MDEyOk9yZ2FuaXphdGlvbjUyODg2MA==", "avatar_url": "https://avatars.githubusercontent.com/u/528860?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bitcoin", "html_url": "https://github.com/bitcoin", "followers_url": "https://api.github.com/users/bitcoin/followers", "following_url": "https://api.github.com/users/bitcoin/following{/other_user}", "gists_url": "https://api.github.com/users/bitcoin/gists{/gist_id}", "starred_url": "https://api.github.com/users/bitcoin/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bitcoin/subscriptions", "organizations_url": "https://api.github.com/users/bitcoin/orgs", "repos_url": "https://api.github.com/users/bitcoin/repos", "events_url": "https://api.github.com/users/bitcoin/events{/privacy}", "received_events_url": "https://api.github.com/users/bitcoin/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/bitcoin/bitcoin", "description": "Bitcoin Core integration/staging tree", "fork": false, "url": "https://api.github.com/repos/bitcoin/bitcoin", "forks_url": "https://api.github.com/repos/bitcoin/bitcoin/forks", "keys_url": "https://api.github.com/repos/bitcoin/bitcoin/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/bitcoin/bitcoin/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/bitcoin/bitcoin/teams", "hooks_url": "https://api.github.com/repos/bitcoin/bitcoin/hooks", "issue_events_url": "https://api.github.com/repos/bitcoin/bitcoin/issues/events{/number}", "events_url": "https://api.github.com/repos/bitcoin/bitcoin/events", "assignees_url": "https://api.github.com/repos/bitcoin/bitcoin/assignees{/user}", "branches_url": "https://api.github.com/repos/bitcoin/bitcoin/branches{/branch}", "tags_url": "https://api.github.com/repos/bitcoin/bitcoin/tags", "blobs_url": "https://api.github.com/repos/bitcoin/bitcoin/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/bitcoin/bitcoin/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/bitcoin/bitcoin/git/refs{/sha}", "trees_url": "https://api.github.com/repos/bitcoin/bitcoin/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/bitcoin/bitcoin/statuses/{sha}", "languages_url": "https://api.github.com/repos/bitcoin/bitcoin/languages", "stargazers_url": "https://api.github.com/repos/bitcoin/bitcoin/stargazers", "contributors_url": "https://api.github.com/repos/bitcoin/bitcoin/contributors", "subscribers_url": "https://api.github.com/repos/bitcoin/bitcoin/subscribers", "subscription_url": "https://api.github.com/repos/bitcoin/bitcoin/subscription", "commits_url": "https://api.github.com/repos/bitcoin/bitcoin/commits{/sha}", "git_commits_url": "https://api.github.com/repos/bitcoin/bitcoin/git/commits{/sha}", "comments_url": "https://api.github.com/repos/bitcoin/bitcoin/comments{/number}", "issue_comment_url": "https://api.github.com/repos/bitcoin/bitcoin/issues/comments{/number}", "contents_url": "https://api.github.com/repos/bitcoin/bitcoin/contents/{+path}", "compare_url": "https://api.github.com/repos/bitcoin/bitcoin/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/bitcoin/bitcoin/merges", "archive_url": "https://api.github.com/repos/bitcoin/bitcoin/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/bitcoin/bitcoin/downloads", "issues_url": "https://api.github.com/repos/bitcoin/bitcoin/issues{/number}", "pulls_url": "https://api.github.com/repos/bitcoin/bitcoin/pulls{/number}", "milestones_url": "https://api.github.com/repos/bitcoin/bitcoin/milestones{/number}", "notifications_url": "https://api.github.com/repos/bitcoin/bitcoin/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/bitcoin/bitcoin/labels{/name}", "releases_url": "https://api.github.com/repos/bitcoin/bitcoin/releases{/id}", "deployments_url": "https://api.github.com/repos/bitcoin/bitcoin/deployments", "created_at": "2010-12-19T15:16:43Z", "updated_at": "2026-08-04T05:55:05Z", "pushed_at": "2026-08-03T14:53:28Z", "git_url": "git://github.com/bitcoin/bitcoin.git", "ssh_url": "git@github.com:bitcoin/bitcoin.git", "clone_url": "https://github.com/bitcoin/bitcoin.git", "svn_url": "https://github.com/bitcoin/bitcoin", "homepage": "https://bitcoincore.org/en/download", "size": 321131, "stargazers_count": 89767, "watchers_count": 89767, "language": "C++", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": false, "has_pages": false, "has_discussions": false, "forks_count": 39229, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 700, "license": {"key": "mit", "name": "MIT License", "spdx_id": "MIT", "url": "https://api.github.com/licenses/mit", "node_id": "MDc6TGljZW5zZTEz"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["bitcoin", "c-plus-plus", "cryptocurrency", "cryptography", "p2p"], "visibility": "public", "forks": 39229, "open_issues": 700, "watchers": 89767, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": false}, "temp_clone_token": "", "custom_properties": {}, "organization": {"login": "bitcoin", "id": 528860, "node_id": "MDEyOk9yZ2FuaXphdGlvbjUyODg2MA==", "avatar_url": "https://avatars.githubusercontent.com/u/528860?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bitcoin", "html_url": "https://github.com/bitcoin", "followers_url": "https://api.github.com/users/bitcoin/followers", "following_url": "https://api.github.com/users/bitcoin/following{/other_user}", "gists_url": "https://api.github.com/users/bitcoin/gists{/gist_id}", "starred_url": "https://api.github.com/users/bitcoin/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bitcoin/subscriptions", "organizations_url": "https://api.github.com/users/bitcoin/orgs", "repos_url": "https://api.github.com/users/bitcoin/repos", "events_url": "https://api.github.com/users/bitcoin/events{/privacy}", "received_events_url": "https://api.github.com/users/bitcoin/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 39229, "subscribers_count": 4101}</t>
         </is>
       </c>
     </row>
@@ -38169,7 +38169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121691+00:00</t>
+          <t>2026-08-04T05:55:39.539689+00:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -38250,7 +38250,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121677+00:00</t>
+          <t>2026-08-04T05:55:39.539678+00:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -38296,7 +38296,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>{"endpoint": "https://api.github.com/repos/bnb-chain/bsc/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-04T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
+          <t>{"endpoint": "https://api.github.com/repos/bnb-chain/bsc/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-05T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
         </is>
       </c>
     </row>
@@ -38412,7 +38412,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.104483+00:00</t>
+          <t>2026-08-04T05:55:39.539668+00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -38458,7 +38458,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>{"id": 265775217, "node_id": "MDEwOlJlcG9zaXRvcnkyNjU3NzUyMTc=", "name": "bsc", "full_name": "bnb-chain/bsc", "private": false, "owner": {"login": "bnb-chain", "id": 45615063, "node_id": "MDEyOk9yZ2FuaXphdGlvbjQ1NjE1MDYz", "avatar_url": "https://avatars.githubusercontent.com/u/45615063?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bnb-chain", "html_url": "https://github.com/bnb-chain", "followers_url": "https://api.github.com/users/bnb-chain/followers", "following_url": "https://api.github.com/users/bnb-chain/following{/other_user}", "gists_url": "https://api.github.com/users/bnb-chain/gists{/gist_id}", "starred_url": "https://api.github.com/users/bnb-chain/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bnb-chain/subscriptions", "organizations_url": "https://api.github.com/users/bnb-chain/orgs", "repos_url": "https://api.github.com/users/bnb-chain/repos", "events_url": "https://api.github.com/users/bnb-chain/events{/privacy}", "received_events_url": "https://api.github.com/users/bnb-chain/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/bnb-chain/bsc", "description": "A BNB Smart Chain client based on the go-ethereum fork", "fork": false, "url": "https://api.github.com/repos/bnb-chain/bsc", "forks_url": "https://api.github.com/repos/bnb-chain/bsc/forks", "keys_url": "https://api.github.com/repos/bnb-chain/bsc/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/bnb-chain/bsc/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/bnb-chain/bsc/teams", "hooks_url": "https://api.github.com/repos/bnb-chain/bsc/hooks", "issue_events_url": "https://api.github.com/repos/bnb-chain/bsc/issues/events{/number}", "events_url": "https://api.github.com/repos/bnb-chain/bsc/events", "assignees_url": "https://api.github.com/repos/bnb-chain/bsc/assignees{/user}", "branches_url": "https://api.github.com/repos/bnb-chain/bsc/branches{/branch}", "tags_url": "https://api.github.com/repos/bnb-chain/bsc/tags", "blobs_url": "https://api.github.com/repos/bnb-chain/bsc/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/bnb-chain/bsc/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/bnb-chain/bsc/git/refs{/sha}", "trees_url": "https://api.github.com/repos/bnb-chain/bsc/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/bnb-chain/bsc/statuses/{sha}", "languages_url": "https://api.github.com/repos/bnb-chain/bsc/languages", "stargazers_url": "https://api.github.com/repos/bnb-chain/bsc/stargazers", "contributors_url": "https://api.github.com/repos/bnb-chain/bsc/contributors", "subscribers_url": "https://api.github.com/repos/bnb-chain/bsc/subscribers", "subscription_url": "https://api.github.com/repos/bnb-chain/bsc/subscription", "commits_url": "https://api.github.com/repos/bnb-chain/bsc/commits{/sha}", "git_commits_url": "https://api.github.com/repos/bnb-chain/bsc/git/commits{/sha}", "comments_url": "https://api.github.com/repos/bnb-chain/bsc/comments{/number}", "issue_comment_url": "https://api.github.com/repos/bnb-chain/bsc/issues/comments{/number}", "contents_url": "https://api.github.com/repos/bnb-chain/bsc/contents/{+path}", "compare_url": "https://api.github.com/repos/bnb-chain/bsc/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/bnb-chain/bsc/merges", "archive_url": "https://api.github.com/repos/bnb-chain/bsc/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/bnb-chain/bsc/downloads", "issues_url": "https://api.github.com/repos/bnb-chain/bsc/issues{/number}", "pulls_url": "https://api.github.com/repos/bnb-chain/bsc/pulls{/number}", "milestones_url": "https://api.github.com/repos/bnb-chain/bsc/milestones{/number}", "notifications_url": "https://api.github.com/repos/bnb-chain/bsc/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/bnb-chain/bsc/labels{/name}", "releases_url": "https://api.github.com/repos/bnb-chain/bsc/releases{/id}", "deployments_url": "https://api.github.com/repos/bnb-chain/bsc/deployments", "created_at": "2020-05-21T06:44:14Z", "updated_at": "2026-08-02T17:31:25Z", "pushed_at": "2026-07-31T02:10:39Z", "git_url": "git://github.com/bnb-chain/bsc.git", "ssh_url": "git@github.com:bnb-chain/bsc.git", "clone_url": "https://github.com/bnb-chain/bsc.git", "svn_url": "https://github.com/bnb-chain/bsc", "homepage": "", "size": 269863, "stargazers_count": 3273, "watchers_count": 3273, "language": "Go", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": true, "has_pages": false, "has_discussions": true, "forks_count": 1809, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 20, "license": {"key": "lgpl-3.0", "name": "GNU Lesser General Public License v3.0", "spdx_id": "LGPL-3.0", "url": "https://api.github.com/licenses/lgpl-3.0", "node_id": "MDc6TGljZW5zZTEy"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["blockchain", "bnb", "ethereum"], "visibility": "public", "forks": 1809, "open_issues": 20, "watchers": 3273, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": true}, "custom_properties": {}, "organization": {"login": "bnb-chain", "id": 45615063, "node_id": "MDEyOk9yZ2FuaXphdGlvbjQ1NjE1MDYz", "avatar_url": "https://avatars.githubusercontent.com/u/45615063?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bnb-chain", "html_url": "https://github.com/bnb-chain", "followers_url": "https://api.github.com/users/bnb-chain/followers", "following_url": "https://api.github.com/users/bnb-chain/following{/other_user}", "gists_url": "https://api.github.com/users/bnb-chain/gists{/gist_id}", "starred_url": "https://api.github.com/users/bnb-chain/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bnb-chain/subscriptions", "organizations_url": "https://api.github.com/users/bnb-chain/orgs", "repos_url": "https://api.github.com/users/bnb-chain/repos", "events_url": "https://api.github.com/users/bnb-chain/events{/privacy}", "received_events_url": "https://api.github.com/users/bnb-chain/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 1809, "subscribers_count": 119}</t>
+          <t>{"id": 265775217, "node_id": "MDEwOlJlcG9zaXRvcnkyNjU3NzUyMTc=", "name": "bsc", "full_name": "bnb-chain/bsc", "private": false, "owner": {"login": "bnb-chain", "id": 45615063, "node_id": "MDEyOk9yZ2FuaXphdGlvbjQ1NjE1MDYz", "avatar_url": "https://avatars.githubusercontent.com/u/45615063?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bnb-chain", "html_url": "https://github.com/bnb-chain", "followers_url": "https://api.github.com/users/bnb-chain/followers", "following_url": "https://api.github.com/users/bnb-chain/following{/other_user}", "gists_url": "https://api.github.com/users/bnb-chain/gists{/gist_id}", "starred_url": "https://api.github.com/users/bnb-chain/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bnb-chain/subscriptions", "organizations_url": "https://api.github.com/users/bnb-chain/orgs", "repos_url": "https://api.github.com/users/bnb-chain/repos", "events_url": "https://api.github.com/users/bnb-chain/events{/privacy}", "received_events_url": "https://api.github.com/users/bnb-chain/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/bnb-chain/bsc", "description": "A BNB Smart Chain client based on the go-ethereum fork", "fork": false, "url": "https://api.github.com/repos/bnb-chain/bsc", "forks_url": "https://api.github.com/repos/bnb-chain/bsc/forks", "keys_url": "https://api.github.com/repos/bnb-chain/bsc/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/bnb-chain/bsc/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/bnb-chain/bsc/teams", "hooks_url": "https://api.github.com/repos/bnb-chain/bsc/hooks", "issue_events_url": "https://api.github.com/repos/bnb-chain/bsc/issues/events{/number}", "events_url": "https://api.github.com/repos/bnb-chain/bsc/events", "assignees_url": "https://api.github.com/repos/bnb-chain/bsc/assignees{/user}", "branches_url": "https://api.github.com/repos/bnb-chain/bsc/branches{/branch}", "tags_url": "https://api.github.com/repos/bnb-chain/bsc/tags", "blobs_url": "https://api.github.com/repos/bnb-chain/bsc/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/bnb-chain/bsc/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/bnb-chain/bsc/git/refs{/sha}", "trees_url": "https://api.github.com/repos/bnb-chain/bsc/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/bnb-chain/bsc/statuses/{sha}", "languages_url": "https://api.github.com/repos/bnb-chain/bsc/languages", "stargazers_url": "https://api.github.com/repos/bnb-chain/bsc/stargazers", "contributors_url": "https://api.github.com/repos/bnb-chain/bsc/contributors", "subscribers_url": "https://api.github.com/repos/bnb-chain/bsc/subscribers", "subscription_url": "https://api.github.com/repos/bnb-chain/bsc/subscription", "commits_url": "https://api.github.com/repos/bnb-chain/bsc/commits{/sha}", "git_commits_url": "https://api.github.com/repos/bnb-chain/bsc/git/commits{/sha}", "comments_url": "https://api.github.com/repos/bnb-chain/bsc/comments{/number}", "issue_comment_url": "https://api.github.com/repos/bnb-chain/bsc/issues/comments{/number}", "contents_url": "https://api.github.com/repos/bnb-chain/bsc/contents/{+path}", "compare_url": "https://api.github.com/repos/bnb-chain/bsc/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/bnb-chain/bsc/merges", "archive_url": "https://api.github.com/repos/bnb-chain/bsc/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/bnb-chain/bsc/downloads", "issues_url": "https://api.github.com/repos/bnb-chain/bsc/issues{/number}", "pulls_url": "https://api.github.com/repos/bnb-chain/bsc/pulls{/number}", "milestones_url": "https://api.github.com/repos/bnb-chain/bsc/milestones{/number}", "notifications_url": "https://api.github.com/repos/bnb-chain/bsc/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/bnb-chain/bsc/labels{/name}", "releases_url": "https://api.github.com/repos/bnb-chain/bsc/releases{/id}", "deployments_url": "https://api.github.com/repos/bnb-chain/bsc/deployments", "created_at": "2020-05-21T06:44:14Z", "updated_at": "2026-08-02T17:31:25Z", "pushed_at": "2026-07-31T02:10:39Z", "git_url": "git://github.com/bnb-chain/bsc.git", "ssh_url": "git@github.com:bnb-chain/bsc.git", "clone_url": "https://github.com/bnb-chain/bsc.git", "svn_url": "https://github.com/bnb-chain/bsc", "homepage": "", "size": 269863, "stargazers_count": 3273, "watchers_count": 3273, "language": "Go", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": true, "has_pages": false, "has_discussions": true, "forks_count": 1809, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 20, "license": {"key": "lgpl-3.0", "name": "GNU Lesser General Public License v3.0", "spdx_id": "LGPL-3.0", "url": "https://api.github.com/licenses/lgpl-3.0", "node_id": "MDc6TGljZW5zZTEy"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["blockchain", "bnb", "ethereum"], "visibility": "public", "forks": 1809, "open_issues": 20, "watchers": 3273, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": false}, "temp_clone_token": "", "custom_properties": {}, "organization": {"login": "bnb-chain", "id": 45615063, "node_id": "MDEyOk9yZ2FuaXphdGlvbjQ1NjE1MDYz", "avatar_url": "https://avatars.githubusercontent.com/u/45615063?v=4", "gravatar_id": "", "url": "https://api.github.com/users/bnb-chain", "html_url": "https://github.com/bnb-chain", "followers_url": "https://api.github.com/users/bnb-chain/followers", "following_url": "https://api.github.com/users/bnb-chain/following{/other_user}", "gists_url": "https://api.github.com/users/bnb-chain/gists{/gist_id}", "starred_url": "https://api.github.com/users/bnb-chain/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/bnb-chain/subscriptions", "organizations_url": "https://api.github.com/users/bnb-chain/orgs", "repos_url": "https://api.github.com/users/bnb-chain/repos", "events_url": "https://api.github.com/users/bnb-chain/events{/privacy}", "received_events_url": "https://api.github.com/users/bnb-chain/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 1809, "subscribers_count": 119}</t>
         </is>
       </c>
     </row>
@@ -38493,7 +38493,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121653+00:00</t>
+          <t>2026-08-04T05:55:39.539660+00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -38574,7 +38574,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121639+00:00</t>
+          <t>2026-08-04T05:55:39.539650+00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -38620,7 +38620,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>{"endpoint": "https://api.github.com/repos/ethereum/go-ethereum/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-04T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
+          <t>{"endpoint": "https://api.github.com/repos/ethereum/go-ethereum/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-05T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
         </is>
       </c>
     </row>
@@ -38736,7 +38736,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.104483+00:00</t>
+          <t>2026-08-04T05:55:39.539639+00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -38782,7 +38782,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>{"id": 15452919, "node_id": "MDEwOlJlcG9zaXRvcnkxNTQ1MjkxOQ==", "name": "go-ethereum", "full_name": "ethereum/go-ethereum", "private": false, "owner": {"login": "ethereum", "id": 6250754, "node_id": "MDEyOk9yZ2FuaXphdGlvbjYyNTA3NTQ=", "avatar_url": "https://avatars.githubusercontent.com/u/6250754?v=4", "gravatar_id": "", "url": "https://api.github.com/users/ethereum", "html_url": "https://github.com/ethereum", "followers_url": "https://api.github.com/users/ethereum/followers", "following_url": "https://api.github.com/users/ethereum/following{/other_user}", "gists_url": "https://api.github.com/users/ethereum/gists{/gist_id}", "starred_url": "https://api.github.com/users/ethereum/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/ethereum/subscriptions", "organizations_url": "https://api.github.com/users/ethereum/orgs", "repos_url": "https://api.github.com/users/ethereum/repos", "events_url": "https://api.github.com/users/ethereum/events{/privacy}", "received_events_url": "https://api.github.com/users/ethereum/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/ethereum/go-ethereum", "description": "Go implementation of the Ethereum protocol", "fork": false, "url": "https://api.github.com/repos/ethereum/go-ethereum", "forks_url": "https://api.github.com/repos/ethereum/go-ethereum/forks", "keys_url": "https://api.github.com/repos/ethereum/go-ethereum/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/ethereum/go-ethereum/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/ethereum/go-ethereum/teams", "hooks_url": "https://api.github.com/repos/ethereum/go-ethereum/hooks", "issue_events_url": "https://api.github.com/repos/ethereum/go-ethereum/issues/events{/number}", "events_url": "https://api.github.com/repos/ethereum/go-ethereum/events", "assignees_url": "https://api.github.com/repos/ethereum/go-ethereum/assignees{/user}", "branches_url": "https://api.github.com/repos/ethereum/go-ethereum/branches{/branch}", "tags_url": "https://api.github.com/repos/ethereum/go-ethereum/tags", "blobs_url": "https://api.github.com/repos/ethereum/go-ethereum/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/ethereum/go-ethereum/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/ethereum/go-ethereum/git/refs{/sha}", "trees_url": "https://api.github.com/repos/ethereum/go-ethereum/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/ethereum/go-ethereum/statuses/{sha}", "languages_url": "https://api.github.com/repos/ethereum/go-ethereum/languages", "stargazers_url": "https://api.github.com/repos/ethereum/go-ethereum/stargazers", "contributors_url": "https://api.github.com/repos/ethereum/go-ethereum/contributors", "subscribers_url": "https://api.github.com/repos/ethereum/go-ethereum/subscribers", "subscription_url": "https://api.github.com/repos/ethereum/go-ethereum/subscription", "commits_url": "https://api.github.com/repos/ethereum/go-ethereum/commits{/sha}", "git_commits_url": "https://api.github.com/repos/ethereum/go-ethereum/git/commits{/sha}", "comments_url": "https://api.github.com/repos/ethereum/go-ethereum/comments{/number}", "issue_comment_url": "https://api.github.com/repos/ethereum/go-ethereum/issues/comments{/number}", "contents_url": "https://api.github.com/repos/ethereum/go-ethereum/contents/{+path}", "compare_url": "https://api.github.com/repos/ethereum/go-ethereum/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/ethereum/go-ethereum/merges", "archive_url": "https://api.github.com/repos/ethereum/go-ethereum/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/ethereum/go-ethereum/downloads", "issues_url": "https://api.github.com/repos/ethereum/go-ethereum/issues{/number}", "pulls_url": "https://api.github.com/repos/ethereum/go-ethereum/pulls{/number}", "milestones_url": "https://api.github.com/repos/ethereum/go-ethereum/milestones{/number}", "notifications_url": "https://api.github.com/repos/ethereum/go-ethereum/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/ethereum/go-ethereum/labels{/name}", "releases_url": "https://api.github.com/repos/ethereum/go-ethereum/releases{/id}", "deployments_url": "https://api.github.com/repos/ethereum/go-ethereum/deployments", "created_at": "2013-12-26T13:05:46Z", "updated_at": "2026-08-03T15:33:41Z", "pushed_at": "2026-08-03T10:36:39Z", "git_url": "git://github.com/ethereum/go-ethereum.git", "ssh_url": "git@github.com:ethereum/go-ethereum.git", "clone_url": "https://github.com/ethereum/go-ethereum.git", "svn_url": "https://github.com/ethereum/go-ethereum", "homepage": "https://geth.ethereum.org", "size": 238690, "stargazers_count": 51269, "watchers_count": 51269, "language": "Go", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": true, "has_pages": true, "has_discussions": false, "forks_count": 22088, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 400, "license": {"key": "lgpl-3.0", "name": "GNU Lesser General Public License v3.0", "spdx_id": "LGPL-3.0", "url": "https://api.github.com/licenses/lgpl-3.0", "node_id": "MDc6TGljZW5zZTEy"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["blockchain", "ethereum", "geth", "go", "p2p"], "visibility": "public", "forks": 22088, "open_issues": 400, "watchers": 51269, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": true}, "custom_properties": {"last_reviewed": "2020-01-01", "team": ["to be defined"]}, "organization": {"login": "ethereum", "id": 6250754, "node_id": "MDEyOk9yZ2FuaXphdGlvbjYyNTA3NTQ=", "avatar_url": "https://avatars.githubusercontent.com/u/6250754?v=4", "gravatar_id": "", "url": "https://api.github.com/users/ethereum", "html_url": "https://github.com/ethereum", "followers_url": "https://api.github.com/users/ethereum/followers", "following_url": "https://api.github.com/users/ethereum/following{/other_user}", "gists_url": "https://api.github.com/users/ethereum/gists{/gist_id}", "starred_url": "https://api.github.com/users/ethereum/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/ethereum/subscriptions", "organizations_url": "https://api.github.com/users/ethereum/orgs", "repos_url": "https://api.github.com/users/ethereum/repos", "events_url": "https://api.github.com/users/ethereum/events{/privacy}", "received_events_url": "https://api.github.com/users/ethereum/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 22088, "subscribers_count": 2230}</t>
+          <t>{"id": 15452919, "node_id": "MDEwOlJlcG9zaXRvcnkxNTQ1MjkxOQ==", "name": "go-ethereum", "full_name": "ethereum/go-ethereum", "private": false, "owner": {"login": "ethereum", "id": 6250754, "node_id": "MDEyOk9yZ2FuaXphdGlvbjYyNTA3NTQ=", "avatar_url": "https://avatars.githubusercontent.com/u/6250754?v=4", "gravatar_id": "", "url": "https://api.github.com/users/ethereum", "html_url": "https://github.com/ethereum", "followers_url": "https://api.github.com/users/ethereum/followers", "following_url": "https://api.github.com/users/ethereum/following{/other_user}", "gists_url": "https://api.github.com/users/ethereum/gists{/gist_id}", "starred_url": "https://api.github.com/users/ethereum/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/ethereum/subscriptions", "organizations_url": "https://api.github.com/users/ethereum/orgs", "repos_url": "https://api.github.com/users/ethereum/repos", "events_url": "https://api.github.com/users/ethereum/events{/privacy}", "received_events_url": "https://api.github.com/users/ethereum/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/ethereum/go-ethereum", "description": "Go implementation of the Ethereum protocol", "fork": false, "url": "https://api.github.com/repos/ethereum/go-ethereum", "forks_url": "https://api.github.com/repos/ethereum/go-ethereum/forks", "keys_url": "https://api.github.com/repos/ethereum/go-ethereum/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/ethereum/go-ethereum/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/ethereum/go-ethereum/teams", "hooks_url": "https://api.github.com/repos/ethereum/go-ethereum/hooks", "issue_events_url": "https://api.github.com/repos/ethereum/go-ethereum/issues/events{/number}", "events_url": "https://api.github.com/repos/ethereum/go-ethereum/events", "assignees_url": "https://api.github.com/repos/ethereum/go-ethereum/assignees{/user}", "branches_url": "https://api.github.com/repos/ethereum/go-ethereum/branches{/branch}", "tags_url": "https://api.github.com/repos/ethereum/go-ethereum/tags", "blobs_url": "https://api.github.com/repos/ethereum/go-ethereum/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/ethereum/go-ethereum/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/ethereum/go-ethereum/git/refs{/sha}", "trees_url": "https://api.github.com/repos/ethereum/go-ethereum/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/ethereum/go-ethereum/statuses/{sha}", "languages_url": "https://api.github.com/repos/ethereum/go-ethereum/languages", "stargazers_url": "https://api.github.com/repos/ethereum/go-ethereum/stargazers", "contributors_url": "https://api.github.com/repos/ethereum/go-ethereum/contributors", "subscribers_url": "https://api.github.com/repos/ethereum/go-ethereum/subscribers", "subscription_url": "https://api.github.com/repos/ethereum/go-ethereum/subscription", "commits_url": "https://api.github.com/repos/ethereum/go-ethereum/commits{/sha}", "git_commits_url": "https://api.github.com/repos/ethereum/go-ethereum/git/commits{/sha}", "comments_url": "https://api.github.com/repos/ethereum/go-ethereum/comments{/number}", "issue_comment_url": "https://api.github.com/repos/ethereum/go-ethereum/issues/comments{/number}", "contents_url": "https://api.github.com/repos/ethereum/go-ethereum/contents/{+path}", "compare_url": "https://api.github.com/repos/ethereum/go-ethereum/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/ethereum/go-ethereum/merges", "archive_url": "https://api.github.com/repos/ethereum/go-ethereum/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/ethereum/go-ethereum/downloads", "issues_url": "https://api.github.com/repos/ethereum/go-ethereum/issues{/number}", "pulls_url": "https://api.github.com/repos/ethereum/go-ethereum/pulls{/number}", "milestones_url": "https://api.github.com/repos/ethereum/go-ethereum/milestones{/number}", "notifications_url": "https://api.github.com/repos/ethereum/go-ethereum/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/ethereum/go-ethereum/labels{/name}", "releases_url": "https://api.github.com/repos/ethereum/go-ethereum/releases{/id}", "deployments_url": "https://api.github.com/repos/ethereum/go-ethereum/deployments", "created_at": "2013-12-26T13:05:46Z", "updated_at": "2026-08-04T05:37:02Z", "pushed_at": "2026-08-04T05:54:29Z", "git_url": "git://github.com/ethereum/go-ethereum.git", "ssh_url": "git@github.com:ethereum/go-ethereum.git", "clone_url": "https://github.com/ethereum/go-ethereum.git", "svn_url": "https://github.com/ethereum/go-ethereum", "homepage": "https://geth.ethereum.org", "size": 238788, "stargazers_count": 51264, "watchers_count": 51264, "language": "Go", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": true, "has_pages": true, "has_discussions": false, "forks_count": 22088, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 398, "license": {"key": "lgpl-3.0", "name": "GNU Lesser General Public License v3.0", "spdx_id": "LGPL-3.0", "url": "https://api.github.com/licenses/lgpl-3.0", "node_id": "MDc6TGljZW5zZTEy"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["blockchain", "ethereum", "geth", "go", "p2p"], "visibility": "public", "forks": 22088, "open_issues": 398, "watchers": 51264, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": false}, "temp_clone_token": "", "custom_properties": {"last_reviewed": "2020-01-01", "team": ["to be defined"]}, "organization": {"login": "ethereum", "id": 6250754, "node_id": "MDEyOk9yZ2FuaXphdGlvbjYyNTA3NTQ=", "avatar_url": "https://avatars.githubusercontent.com/u/6250754?v=4", "gravatar_id": "", "url": "https://api.github.com/users/ethereum", "html_url": "https://github.com/ethereum", "followers_url": "https://api.github.com/users/ethereum/followers", "following_url": "https://api.github.com/users/ethereum/following{/other_user}", "gists_url": "https://api.github.com/users/ethereum/gists{/gist_id}", "starred_url": "https://api.github.com/users/ethereum/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/ethereum/subscriptions", "organizations_url": "https://api.github.com/users/ethereum/orgs", "repos_url": "https://api.github.com/users/ethereum/repos", "events_url": "https://api.github.com/users/ethereum/events{/privacy}", "received_events_url": "https://api.github.com/users/ethereum/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 22088, "subscribers_count": 2231}</t>
         </is>
       </c>
     </row>
@@ -38817,7 +38817,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121720+00:00</t>
+          <t>2026-08-04T05:55:39.539714+00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121712+00:00</t>
+          <t>2026-08-04T05:55:39.539708+00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -38944,7 +38944,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>{"endpoint": "https://api.github.com/repos/ripple/rippled/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-04T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
+          <t>{"endpoint": "https://api.github.com/repos/ripple/rippled/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-05T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
         </is>
       </c>
     </row>
@@ -39060,7 +39060,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.104483+00:00</t>
+          <t>2026-08-04T05:55:39.539699+00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -39106,7 +39106,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>{"id": 2724167, "node_id": "MDEwOlJlcG9zaXRvcnkyNzI0MTY3", "name": "rippled", "full_name": "XRPLF/rippled", "private": false, "owner": {"login": "XRPLF", "id": 67929741, "node_id": "MDEyOk9yZ2FuaXphdGlvbjY3OTI5NzQx", "avatar_url": "https://avatars.githubusercontent.com/u/67929741?v=4", "gravatar_id": "", "url": "https://api.github.com/users/XRPLF", "html_url": "https://github.com/XRPLF", "followers_url": "https://api.github.com/users/XRPLF/followers", "following_url": "https://api.github.com/users/XRPLF/following{/other_user}", "gists_url": "https://api.github.com/users/XRPLF/gists{/gist_id}", "starred_url": "https://api.github.com/users/XRPLF/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/XRPLF/subscriptions", "organizations_url": "https://api.github.com/users/XRPLF/orgs", "repos_url": "https://api.github.com/users/XRPLF/repos", "events_url": "https://api.github.com/users/XRPLF/events{/privacy}", "received_events_url": "https://api.github.com/users/XRPLF/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/XRPLF/rippled", "description": "Decentralized cryptocurrency blockchain daemon implementing the XRP Ledger protocol in C++", "fork": false, "url": "https://api.github.com/repos/XRPLF/rippled", "forks_url": "https://api.github.com/repos/XRPLF/rippled/forks", "keys_url": "https://api.github.com/repos/XRPLF/rippled/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/XRPLF/rippled/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/XRPLF/rippled/teams", "hooks_url": "https://api.github.com/repos/XRPLF/rippled/hooks", "issue_events_url": "https://api.github.com/repos/XRPLF/rippled/issues/events{/number}", "events_url": "https://api.github.com/repos/XRPLF/rippled/events", "assignees_url": "https://api.github.com/repos/XRPLF/rippled/assignees{/user}", "branches_url": "https://api.github.com/repos/XRPLF/rippled/branches{/branch}", "tags_url": "https://api.github.com/repos/XRPLF/rippled/tags", "blobs_url": "https://api.github.com/repos/XRPLF/rippled/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/XRPLF/rippled/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/XRPLF/rippled/git/refs{/sha}", "trees_url": "https://api.github.com/repos/XRPLF/rippled/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/XRPLF/rippled/statuses/{sha}", "languages_url": "https://api.github.com/repos/XRPLF/rippled/languages", "stargazers_url": "https://api.github.com/repos/XRPLF/rippled/stargazers", "contributors_url": "https://api.github.com/repos/XRPLF/rippled/contributors", "subscribers_url": "https://api.github.com/repos/XRPLF/rippled/subscribers", "subscription_url": "https://api.github.com/repos/XRPLF/rippled/subscription", "commits_url": "https://api.github.com/repos/XRPLF/rippled/commits{/sha}", "git_commits_url": "https://api.github.com/repos/XRPLF/rippled/git/commits{/sha}", "comments_url": "https://api.github.com/repos/XRPLF/rippled/comments{/number}", "issue_comment_url": "https://api.github.com/repos/XRPLF/rippled/issues/comments{/number}", "contents_url": "https://api.github.com/repos/XRPLF/rippled/contents/{+path}", "compare_url": "https://api.github.com/repos/XRPLF/rippled/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/XRPLF/rippled/merges", "archive_url": "https://api.github.com/repos/XRPLF/rippled/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/XRPLF/rippled/downloads", "issues_url": "https://api.github.com/repos/XRPLF/rippled/issues{/number}", "pulls_url": "https://api.github.com/repos/XRPLF/rippled/pulls{/number}", "milestones_url": "https://api.github.com/repos/XRPLF/rippled/milestones{/number}", "notifications_url": "https://api.github.com/repos/XRPLF/rippled/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/XRPLF/rippled/labels{/name}", "releases_url": "https://api.github.com/repos/XRPLF/rippled/releases{/id}", "deployments_url": "https://api.github.com/repos/XRPLF/rippled/deployments", "created_at": "2011-11-07T04:40:15Z", "updated_at": "2026-08-03T06:42:03Z", "pushed_at": "2026-08-03T17:48:33Z", "git_url": "git://github.com/XRPLF/rippled.git", "ssh_url": "git@github.com:XRPLF/rippled.git", "clone_url": "https://github.com/XRPLF/rippled.git", "svn_url": "https://github.com/XRPLF/rippled", "homepage": "https://xrpl.org", "size": 186636, "stargazers_count": 5177, "watchers_count": 5177, "language": "C++", "has_issues": true, "has_projects": false, "has_downloads": false, "has_wiki": true, "has_pages": true, "has_discussions": true, "forks_count": 1696, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 958, "license": {"key": "isc", "name": "ISC License", "spdx_id": "ISC", "url": "https://api.github.com/licenses/isc", "node_id": "MDc6TGljZW5zZTEw"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["blockchain", "c-plus-plus", "cplusplus", "cryptography", "xrp", "xrp-ledger", "xrpl"], "visibility": "public", "forks": 1696, "open_issues": 958, "watchers": 5177, "default_branch": "develop", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": true}, "custom_properties": {}, "organization": {"login": "XRPLF", "id": 67929741, "node_id": "MDEyOk9yZ2FuaXphdGlvbjY3OTI5NzQx", "avatar_url": "https://avatars.githubusercontent.com/u/67929741?v=4", "gravatar_id": "", "url": "https://api.github.com/users/XRPLF", "html_url": "https://github.com/XRPLF", "followers_url": "https://api.github.com/users/XRPLF/followers", "following_url": "https://api.github.com/users/XRPLF/following{/other_user}", "gists_url": "https://api.github.com/users/XRPLF/gists{/gist_id}", "starred_url": "https://api.github.com/users/XRPLF/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/XRPLF/subscriptions", "organizations_url": "https://api.github.com/users/XRPLF/orgs", "repos_url": "https://api.github.com/users/XRPLF/repos", "events_url": "https://api.github.com/users/XRPLF/events{/privacy}", "received_events_url": "https://api.github.com/users/XRPLF/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 1696, "subscribers_count": 506}</t>
+          <t>{"id": 2724167, "node_id": "MDEwOlJlcG9zaXRvcnkyNzI0MTY3", "name": "rippled", "full_name": "XRPLF/rippled", "private": false, "owner": {"login": "XRPLF", "id": 67929741, "node_id": "MDEyOk9yZ2FuaXphdGlvbjY3OTI5NzQx", "avatar_url": "https://avatars.githubusercontent.com/u/67929741?v=4", "gravatar_id": "", "url": "https://api.github.com/users/XRPLF", "html_url": "https://github.com/XRPLF", "followers_url": "https://api.github.com/users/XRPLF/followers", "following_url": "https://api.github.com/users/XRPLF/following{/other_user}", "gists_url": "https://api.github.com/users/XRPLF/gists{/gist_id}", "starred_url": "https://api.github.com/users/XRPLF/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/XRPLF/subscriptions", "organizations_url": "https://api.github.com/users/XRPLF/orgs", "repos_url": "https://api.github.com/users/XRPLF/repos", "events_url": "https://api.github.com/users/XRPLF/events{/privacy}", "received_events_url": "https://api.github.com/users/XRPLF/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/XRPLF/rippled", "description": "Decentralized cryptocurrency blockchain daemon implementing the XRP Ledger protocol in C++", "fork": false, "url": "https://api.github.com/repos/XRPLF/rippled", "forks_url": "https://api.github.com/repos/XRPLF/rippled/forks", "keys_url": "https://api.github.com/repos/XRPLF/rippled/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/XRPLF/rippled/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/XRPLF/rippled/teams", "hooks_url": "https://api.github.com/repos/XRPLF/rippled/hooks", "issue_events_url": "https://api.github.com/repos/XRPLF/rippled/issues/events{/number}", "events_url": "https://api.github.com/repos/XRPLF/rippled/events", "assignees_url": "https://api.github.com/repos/XRPLF/rippled/assignees{/user}", "branches_url": "https://api.github.com/repos/XRPLF/rippled/branches{/branch}", "tags_url": "https://api.github.com/repos/XRPLF/rippled/tags", "blobs_url": "https://api.github.com/repos/XRPLF/rippled/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/XRPLF/rippled/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/XRPLF/rippled/git/refs{/sha}", "trees_url": "https://api.github.com/repos/XRPLF/rippled/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/XRPLF/rippled/statuses/{sha}", "languages_url": "https://api.github.com/repos/XRPLF/rippled/languages", "stargazers_url": "https://api.github.com/repos/XRPLF/rippled/stargazers", "contributors_url": "https://api.github.com/repos/XRPLF/rippled/contributors", "subscribers_url": "https://api.github.com/repos/XRPLF/rippled/subscribers", "subscription_url": "https://api.github.com/repos/XRPLF/rippled/subscription", "commits_url": "https://api.github.com/repos/XRPLF/rippled/commits{/sha}", "git_commits_url": "https://api.github.com/repos/XRPLF/rippled/git/commits{/sha}", "comments_url": "https://api.github.com/repos/XRPLF/rippled/comments{/number}", "issue_comment_url": "https://api.github.com/repos/XRPLF/rippled/issues/comments{/number}", "contents_url": "https://api.github.com/repos/XRPLF/rippled/contents/{+path}", "compare_url": "https://api.github.com/repos/XRPLF/rippled/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/XRPLF/rippled/merges", "archive_url": "https://api.github.com/repos/XRPLF/rippled/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/XRPLF/rippled/downloads", "issues_url": "https://api.github.com/repos/XRPLF/rippled/issues{/number}", "pulls_url": "https://api.github.com/repos/XRPLF/rippled/pulls{/number}", "milestones_url": "https://api.github.com/repos/XRPLF/rippled/milestones{/number}", "notifications_url": "https://api.github.com/repos/XRPLF/rippled/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/XRPLF/rippled/labels{/name}", "releases_url": "https://api.github.com/repos/XRPLF/rippled/releases{/id}", "deployments_url": "https://api.github.com/repos/XRPLF/rippled/deployments", "created_at": "2011-11-07T04:40:15Z", "updated_at": "2026-08-03T21:59:33Z", "pushed_at": "2026-08-04T04:07:10Z", "git_url": "git://github.com/XRPLF/rippled.git", "ssh_url": "git@github.com:XRPLF/rippled.git", "clone_url": "https://github.com/XRPLF/rippled.git", "svn_url": "https://github.com/XRPLF/rippled", "homepage": "https://xrpl.org", "size": 186732, "stargazers_count": 5177, "watchers_count": 5177, "language": "C++", "has_issues": true, "has_projects": false, "has_downloads": false, "has_wiki": true, "has_pages": true, "has_discussions": true, "forks_count": 1696, "mirror_url": null, "archived": false, "disabled": false, "open_issues_count": 961, "license": {"key": "isc", "name": "ISC License", "spdx_id": "ISC", "url": "https://api.github.com/licenses/isc", "node_id": "MDc6TGljZW5zZTEw"}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["blockchain", "c-plus-plus", "cplusplus", "cryptography", "xrp", "xrp-ledger", "xrpl"], "visibility": "public", "forks": 1696, "open_issues": 961, "watchers": 5177, "default_branch": "develop", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": false}, "temp_clone_token": "", "custom_properties": {}, "organization": {"login": "XRPLF", "id": 67929741, "node_id": "MDEyOk9yZ2FuaXphdGlvbjY3OTI5NzQx", "avatar_url": "https://avatars.githubusercontent.com/u/67929741?v=4", "gravatar_id": "", "url": "https://api.github.com/users/XRPLF", "html_url": "https://github.com/XRPLF", "followers_url": "https://api.github.com/users/XRPLF/followers", "following_url": "https://api.github.com/users/XRPLF/following{/other_user}", "gists_url": "https://api.github.com/users/XRPLF/gists{/gist_id}", "starred_url": "https://api.github.com/users/XRPLF/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/XRPLF/subscriptions", "organizations_url": "https://api.github.com/users/XRPLF/orgs", "repos_url": "https://api.github.com/users/XRPLF/repos", "events_url": "https://api.github.com/users/XRPLF/events{/privacy}", "received_events_url": "https://api.github.com/users/XRPLF/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 1696, "subscribers_count": 506}</t>
         </is>
       </c>
     </row>
@@ -39141,7 +39141,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121741+00:00</t>
+          <t>2026-08-04T05:55:39.539732+00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -39222,7 +39222,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-03T20:21:06.121733+00:00</t>
+          <t>2026-08-04T05:55:39.539726+00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -39268,7 +39268,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>{"endpoint": "https://api.github.com/repos/solana-labs/solana/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-04T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
+          <t>{"endpoint": "https://api.github.com/repos/solana-labs/solana/commits", "since": "2026-08-03T00:00:00Z", "until": "2026-08-05T00:00:00Z", "per_page": 1, "counted_via": "pagination Link header page count"}</t>
         </is>
       </c>
     </row>
@@ -39384,7 +39384,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-08-03T19:17:46.104483+00:00</t>
+          <t>2026-08-04T05:55:39.539720+00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -39430,7 +39430,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>{"id": 121470383, "node_id": "MDEwOlJlcG9zaXRvcnkxMjE0NzAzODM=", "name": "solana", "full_name": "solana-labs/solana", "private": false, "owner": {"login": "solana-labs", "id": 35608259, "node_id": "MDEyOk9yZ2FuaXphdGlvbjM1NjA4MjU5", "avatar_url": "https://avatars.githubusercontent.com/u/35608259?v=4", "gravatar_id": "", "url": "https://api.github.com/users/solana-labs", "html_url": "https://github.com/solana-labs", "followers_url": "https://api.github.com/users/solana-labs/followers", "following_url": "https://api.github.com/users/solana-labs/following{/other_user}", "gists_url": "https://api.github.com/users/solana-labs/gists{/gist_id}", "starred_url": "https://api.github.com/users/solana-labs/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/solana-labs/subscriptions", "organizations_url": "https://api.github.com/users/solana-labs/orgs", "repos_url": "https://api.github.com/users/solana-labs/repos", "events_url": "https://api.github.com/users/solana-labs/events{/privacy}", "received_events_url": "https://api.github.com/users/solana-labs/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/solana-labs/solana", "description": "Web-Scale Blockchain for fast, secure, scalable, decentralized apps and marketplaces.", "fork": false, "url": "https://api.github.com/repos/solana-labs/solana", "forks_url": "https://api.github.com/repos/solana-labs/solana/forks", "keys_url": "https://api.github.com/repos/solana-labs/solana/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/solana-labs/solana/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/solana-labs/solana/teams", "hooks_url": "https://api.github.com/repos/solana-labs/solana/hooks", "issue_events_url": "https://api.github.com/repos/solana-labs/solana/issues/events{/number}", "events_url": "https://api.github.com/repos/solana-labs/solana/events", "assignees_url": "https://api.github.com/repos/solana-labs/solana/assignees{/user}", "branches_url": "https://api.github.com/repos/solana-labs/solana/branches{/branch}", "tags_url": "https://api.github.com/repos/solana-labs/solana/tags", "blobs_url": "https://api.github.com/repos/solana-labs/solana/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/solana-labs/solana/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/solana-labs/solana/git/refs{/sha}", "trees_url": "https://api.github.com/repos/solana-labs/solana/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/solana-labs/solana/statuses/{sha}", "languages_url": "https://api.github.com/repos/solana-labs/solana/languages", "stargazers_url": "https://api.github.com/repos/solana-labs/solana/stargazers", "contributors_url": "https://api.github.com/repos/solana-labs/solana/contributors", "subscribers_url": "https://api.github.com/repos/solana-labs/solana/subscribers", "subscription_url": "https://api.github.com/repos/solana-labs/solana/subscription", "commits_url": "https://api.github.com/repos/solana-labs/solana/commits{/sha}", "git_commits_url": "https://api.github.com/repos/solana-labs/solana/git/commits{/sha}", "comments_url": "https://api.github.com/repos/solana-labs/solana/comments{/number}", "issue_comment_url": "https://api.github.com/repos/solana-labs/solana/issues/comments{/number}", "contents_url": "https://api.github.com/repos/solana-labs/solana/contents/{+path}", "compare_url": "https://api.github.com/repos/solana-labs/solana/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/solana-labs/solana/merges", "archive_url": "https://api.github.com/repos/solana-labs/solana/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/solana-labs/solana/downloads", "issues_url": "https://api.github.com/repos/solana-labs/solana/issues{/number}", "pulls_url": "https://api.github.com/repos/solana-labs/solana/pulls{/number}", "milestones_url": "https://api.github.com/repos/solana-labs/solana/milestones{/number}", "notifications_url": "https://api.github.com/repos/solana-labs/solana/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/solana-labs/solana/labels{/name}", "releases_url": "https://api.github.com/repos/solana-labs/solana/releases{/id}", "deployments_url": "https://api.github.com/repos/solana-labs/solana/deployments", "created_at": "2018-02-14T04:26:27Z", "updated_at": "2026-08-03T01:13:56Z", "pushed_at": "2025-01-22T19:41:54Z", "git_url": "git://github.com/solana-labs/solana.git", "ssh_url": "git@github.com:solana-labs/solana.git", "clone_url": "https://github.com/solana-labs/solana.git", "svn_url": "https://github.com/solana-labs/solana", "homepage": "https://solanalabs.com", "size": 448781, "stargazers_count": 14945, "watchers_count": 14945, "language": "Rust", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": true, "has_pages": false, "has_discussions": false, "forks_count": 5789, "mirror_url": null, "archived": true, "disabled": false, "open_issues_count": 266, "license": {"key": "apache-2.0", "name": "Apache License 2.0", "spdx_id": "Apache-2.0", "url": "https://api.github.com/licenses/apache-2.0", "node_id": "MDc6TGljZW5zZTI="}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["bitcoin", "blockchain", "ledger", "performance-blockchain", "rust", "rustc", "solana"], "visibility": "public", "forks": 5789, "open_issues": 266, "watchers": 14945, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": true}, "custom_properties": {}, "organization": {"login": "solana-labs", "id": 35608259, "node_id": "MDEyOk9yZ2FuaXphdGlvbjM1NjA4MjU5", "avatar_url": "https://avatars.githubusercontent.com/u/35608259?v=4", "gravatar_id": "", "url": "https://api.github.com/users/solana-labs", "html_url": "https://github.com/solana-labs", "followers_url": "https://api.github.com/users/solana-labs/followers", "following_url": "https://api.github.com/users/solana-labs/following{/other_user}", "gists_url": "https://api.github.com/users/solana-labs/gists{/gist_id}", "starred_url": "https://api.github.com/users/solana-labs/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/solana-labs/subscriptions", "organizations_url": "https://api.github.com/users/solana-labs/orgs", "repos_url": "https://api.github.com/users/solana-labs/repos", "events_url": "https://api.github.com/users/solana-labs/events{/privacy}", "received_events_url": "https://api.github.com/users/solana-labs/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 5789, "subscribers_count": 8}</t>
+          <t>{"id": 121470383, "node_id": "MDEwOlJlcG9zaXRvcnkxMjE0NzAzODM=", "name": "solana", "full_name": "solana-labs/solana", "private": false, "owner": {"login": "solana-labs", "id": 35608259, "node_id": "MDEyOk9yZ2FuaXphdGlvbjM1NjA4MjU5", "avatar_url": "https://avatars.githubusercontent.com/u/35608259?v=4", "gravatar_id": "", "url": "https://api.github.com/users/solana-labs", "html_url": "https://github.com/solana-labs", "followers_url": "https://api.github.com/users/solana-labs/followers", "following_url": "https://api.github.com/users/solana-labs/following{/other_user}", "gists_url": "https://api.github.com/users/solana-labs/gists{/gist_id}", "starred_url": "https://api.github.com/users/solana-labs/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/solana-labs/subscriptions", "organizations_url": "https://api.github.com/users/solana-labs/orgs", "repos_url": "https://api.github.com/users/solana-labs/repos", "events_url": "https://api.github.com/users/solana-labs/events{/privacy}", "received_events_url": "https://api.github.com/users/solana-labs/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "html_url": "https://github.com/solana-labs/solana", "description": "Web-Scale Blockchain for fast, secure, scalable, decentralized apps and marketplaces.", "fork": false, "url": "https://api.github.com/repos/solana-labs/solana", "forks_url": "https://api.github.com/repos/solana-labs/solana/forks", "keys_url": "https://api.github.com/repos/solana-labs/solana/keys{/key_id}", "collaborators_url": "https://api.github.com/repos/solana-labs/solana/collaborators{/collaborator}", "teams_url": "https://api.github.com/repos/solana-labs/solana/teams", "hooks_url": "https://api.github.com/repos/solana-labs/solana/hooks", "issue_events_url": "https://api.github.com/repos/solana-labs/solana/issues/events{/number}", "events_url": "https://api.github.com/repos/solana-labs/solana/events", "assignees_url": "https://api.github.com/repos/solana-labs/solana/assignees{/user}", "branches_url": "https://api.github.com/repos/solana-labs/solana/branches{/branch}", "tags_url": "https://api.github.com/repos/solana-labs/solana/tags", "blobs_url": "https://api.github.com/repos/solana-labs/solana/git/blobs{/sha}", "git_tags_url": "https://api.github.com/repos/solana-labs/solana/git/tags{/sha}", "git_refs_url": "https://api.github.com/repos/solana-labs/solana/git/refs{/sha}", "trees_url": "https://api.github.com/repos/solana-labs/solana/git/trees{/sha}", "statuses_url": "https://api.github.com/repos/solana-labs/solana/statuses/{sha}", "languages_url": "https://api.github.com/repos/solana-labs/solana/languages", "stargazers_url": "https://api.github.com/repos/solana-labs/solana/stargazers", "contributors_url": "https://api.github.com/repos/solana-labs/solana/contributors", "subscribers_url": "https://api.github.com/repos/solana-labs/solana/subscribers", "subscription_url": "https://api.github.com/repos/solana-labs/solana/subscription", "commits_url": "https://api.github.com/repos/solana-labs/solana/commits{/sha}", "git_commits_url": "https://api.github.com/repos/solana-labs/solana/git/commits{/sha}", "comments_url": "https://api.github.com/repos/solana-labs/solana/comments{/number}", "issue_comment_url": "https://api.github.com/repos/solana-labs/solana/issues/comments{/number}", "contents_url": "https://api.github.com/repos/solana-labs/solana/contents/{+path}", "compare_url": "https://api.github.com/repos/solana-labs/solana/compare/{base}...{head}", "merges_url": "https://api.github.com/repos/solana-labs/solana/merges", "archive_url": "https://api.github.com/repos/solana-labs/solana/{archive_format}{/ref}", "downloads_url": "https://api.github.com/repos/solana-labs/solana/downloads", "issues_url": "https://api.github.com/repos/solana-labs/solana/issues{/number}", "pulls_url": "https://api.github.com/repos/solana-labs/solana/pulls{/number}", "milestones_url": "https://api.github.com/repos/solana-labs/solana/milestones{/number}", "notifications_url": "https://api.github.com/repos/solana-labs/solana/notifications{?since,all,participating}", "labels_url": "https://api.github.com/repos/solana-labs/solana/labels{/name}", "releases_url": "https://api.github.com/repos/solana-labs/solana/releases{/id}", "deployments_url": "https://api.github.com/repos/solana-labs/solana/deployments", "created_at": "2018-02-14T04:26:27Z", "updated_at": "2026-08-04T00:11:00Z", "pushed_at": "2025-01-22T19:41:54Z", "git_url": "git://github.com/solana-labs/solana.git", "ssh_url": "git@github.com:solana-labs/solana.git", "clone_url": "https://github.com/solana-labs/solana.git", "svn_url": "https://github.com/solana-labs/solana", "homepage": "https://solanalabs.com", "size": 448781, "stargazers_count": 14944, "watchers_count": 14944, "language": "Rust", "has_issues": true, "has_projects": true, "has_downloads": false, "has_wiki": true, "has_pages": false, "has_discussions": false, "forks_count": 5789, "mirror_url": null, "archived": true, "disabled": false, "open_issues_count": 265, "license": {"key": "apache-2.0", "name": "Apache License 2.0", "spdx_id": "Apache-2.0", "url": "https://api.github.com/licenses/apache-2.0", "node_id": "MDc6TGljZW5zZTI="}, "allow_forking": true, "is_template": false, "web_commit_signoff_required": false, "has_pull_requests": true, "pull_request_creation_policy": "all", "topics": ["bitcoin", "blockchain", "ledger", "performance-blockchain", "rust", "rustc", "solana"], "visibility": "public", "forks": 5789, "open_issues": 265, "watchers": 14944, "default_branch": "master", "permissions": {"admin": false, "maintain": false, "push": false, "triage": false, "pull": false}, "temp_clone_token": "", "custom_properties": {}, "organization": {"login": "solana-labs", "id": 35608259, "node_id": "MDEyOk9yZ2FuaXphdGlvbjM1NjA4MjU5", "avatar_url": "https://avatars.githubusercontent.com/u/35608259?v=4", "gravatar_id": "", "url": "https://api.github.com/users/solana-labs", "html_url": "https://github.com/solana-labs", "followers_url": "https://api.github.com/users/solana-labs/followers", "following_url": "https://api.github.com/users/solana-labs/following{/other_user}", "gists_url": "https://api.github.com/users/solana-labs/gists{/gist_id}", "starred_url": "https://api.github.com/users/solana-labs/starred{/owner}{/repo}", "subscriptions_url": "https://api.github.com/users/solana-labs/subscriptions", "organizations_url": "https://api.github.com/users/solana-labs/orgs", "repos_url": "https://api.github.com/users/solana-labs/repos", "events_url": "https://api.github.com/users/solana-labs/events{/privacy}", "received_events_url": "https://api.github.com/users/solana-labs/received_events", "type": "Organization", "user_view_type": "public", "site_admin": false}, "network_count": 5789, "subscribers_count": 8}</t>
         </is>
       </c>
     </row>
